--- a/Rapportering/DSN/ReportTemplates/MG Mall DsnRegistrering.xlsx
+++ b/Rapportering/DSN/ReportTemplates/MG Mall DsnRegistrering.xlsx
@@ -15,11 +15,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Löpnummer</t>
   </si>
   <si>
+    <t>AgdPerBild</t>
+  </si>
+  <si>
     <t>Projektion</t>
   </si>
   <si>
@@ -32,9 +35,6 @@
     <t>Kompressionstryck</t>
   </si>
   <si>
-    <t>AgdPerBild</t>
-  </si>
-  <si>
     <t>Brösttjocklek</t>
   </si>
   <si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>Filtermaterial</t>
+  </si>
+  <si>
+    <t>Undersökningsteknik</t>
   </si>
   <si>
     <r>
@@ -52,6 +55,26 @@
         <sz val="11"/>
       </rPr>
       <t>Löpnummer</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="11"/>
+      </rPr>
+      <t>AGD</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="11"/>
+      </rPr>
+      <t xml:space="preserve">
+mGy</t>
     </r>
   </si>
   <si>
@@ -115,26 +138,6 @@
         <color rgb="FFFFFFFF"/>
         <sz val="11"/>
       </rPr>
-      <t>AGD</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11"/>
-      </rPr>
-      <t xml:space="preserve">
-mGy</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri"/>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11"/>
-      </rPr>
       <t>Brösttjocklek</t>
     </r>
     <r>
@@ -170,6 +173,17 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="11"/>
+      </rPr>
+      <t>Undersökningsteknik</t>
+    </r>
+  </si>
+  <si>
     <t>LCC</t>
   </si>
   <si>
@@ -179,6 +193,9 @@
     <t>Ag</t>
   </si>
   <si>
+    <t>FFDM_2D</t>
+  </si>
+  <si>
     <t>LMLO</t>
   </si>
   <si>
@@ -186,6 +203,9 @@
   </si>
   <si>
     <t>Al</t>
+  </si>
+  <si>
+    <t>Tomosyntes</t>
   </si>
   <si>
     <t>RCC</t>
@@ -567,17 +587,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="11.85156" customWidth="1"/>
-    <col min="2" max="2" width="10.42188" customWidth="1"/>
-    <col min="3" max="3" width="4.574219" customWidth="1"/>
-    <col min="4" max="4" width="5.003906" customWidth="1"/>
-    <col min="5" max="5" width="23.85156" customWidth="1"/>
-    <col min="6" max="6" width="11.00391" customWidth="1"/>
+    <col min="2" max="2" width="11.00391" customWidth="1"/>
+    <col min="3" max="3" width="10.42188" customWidth="1"/>
+    <col min="4" max="4" width="4.574219" customWidth="1"/>
+    <col min="5" max="5" width="5.003906" customWidth="1"/>
+    <col min="6" max="6" width="23.85156" customWidth="1"/>
     <col min="7" max="7" width="18.71094" customWidth="1"/>
     <col min="8" max="9" width="13.28125" customWidth="1"/>
+    <col min="10" max="10" width="20.00391" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" hidden="1">
@@ -608,336 +629,342 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="F2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="300">
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B3">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B4">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B5">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B6">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B7">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B8">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B9">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B10">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B11">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B12">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B13">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B14">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B15">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B16">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B17">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B18">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B19">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B20">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B21">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B22">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B23">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B24">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B25">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B26">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B27">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B28">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B29">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B30">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B31">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B32">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B33">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B34">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B35">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B36">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B37">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B38">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B39">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B40">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B41">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B42">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B43">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B44">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B45">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B46">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B47">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B48">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B49">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B50">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B51">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B52">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B53">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B54">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B55">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B56">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B57">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B58">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B59">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B60">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B61">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B62">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B63">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B64">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B65">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B66">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B67">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B68">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B69">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B70">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B71">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B72">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B73">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B74">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B75">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B76">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B77">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B78">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B79">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B80">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B81">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B82">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B83">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B84">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B85">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B86">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B87">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B88">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B89">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B90">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B91">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B92">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B93">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B94">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B95">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B96">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B97">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B98">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B99">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B100">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B101">
-      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="B102">
+  <dataValidations count="400">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C3">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C4">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C5">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C6">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C7">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C8">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C9">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C10">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C11">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C12">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C13">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C14">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C15">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C16">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C17">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C18">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C19">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C20">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C21">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C22">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C23">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C24">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C25">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C26">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C27">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C28">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C29">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C30">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C31">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C32">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C33">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C34">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C35">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C36">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C37">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C38">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C39">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C40">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C41">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C42">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C43">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C44">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C45">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C46">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C47">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C48">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C49">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C50">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C51">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C52">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C53">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C54">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C55">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C56">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C57">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C58">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C59">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C60">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C61">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C62">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C63">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C64">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C65">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C66">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C67">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C68">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C69">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C70">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C71">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C72">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C73">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C74">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C75">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C76">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C77">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C78">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C79">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C80">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C81">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C82">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C83">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C84">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C85">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C86">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C87">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C88">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C89">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C90">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C91">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C92">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C93">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C94">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C95">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C96">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C97">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C98">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C99">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C100">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C101">
+      <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj exponeringstyp" sqref="C102">
       <formula1>DSNRegistreringsTabeller!A1:A12</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåtet anodmaterial" sqref="H3">
@@ -1539,6 +1566,306 @@
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåtet filtermaterial" sqref="I102">
       <formula1>DSNRegistreringsTabeller!C1:C4</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J3">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J4">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J5">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J6">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J7">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J8">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J9">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J10">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J11">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J12">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J13">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J14">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J15">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J16">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J17">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J18">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J19">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J20">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J21">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J22">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J23">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J24">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J25">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J26">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J27">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J28">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J29">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J30">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J31">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J32">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J33">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J34">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J35">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J36">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J37">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J38">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J39">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J40">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J41">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J42">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J43">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J44">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J45">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J46">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J47">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J48">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J49">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J50">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J51">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J52">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J53">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J54">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J55">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J56">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J57">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J58">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J59">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J60">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J61">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J62">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J63">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J64">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J65">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J66">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J67">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J68">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J69">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J70">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J71">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J72">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J73">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J74">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J75">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J76">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J77">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J78">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J79">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J80">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J81">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J82">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J83">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J84">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J85">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J86">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J87">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J88">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J89">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J90">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J91">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J92">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J93">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J94">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J95">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J96">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J97">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J98">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J99">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J100">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J101">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Felaktigt värde" error="Välj tillåten undersökningsteknik" sqref="J102">
+      <formula1>DSNRegistreringsTabeller!D1:D2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -1553,83 +1880,89 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
